--- a/database_penyimpanan_aman/database_tkdn_history.xlsx
+++ b/database_penyimpanan_aman/database_tkdn_history.xlsx
@@ -545,7 +545,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-17 18:35:36</t>
+          <t>2026-08-18 08:43:39</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -570,7 +570,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>17 Agustus 2026</t>
+          <t>18 Agustus 2026</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -596,7 +596,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Ir. Ferry Tatimus</t>
+          <t>Ir. Ferry Tatimu</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_tkdn_history.xlsx
+++ b/database_penyimpanan_aman/database_tkdn_history.xlsx
@@ -545,7 +545,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-18 08:43:39</t>
+          <t>2026-08-19 21:14:38</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -570,7 +570,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>18 Agustus 2026</t>
+          <t>19 Agustus 2026</t>
         </is>
       </c>
       <c r="G3" t="n">
